--- a/lcr_analyses/clustering/carriers/LCRFinder/cluster_summaries_hierarchical.xlsx
+++ b/lcr_analyses/clustering/carriers/LCRFinder/cluster_summaries_hierarchical.xlsx
@@ -12,6 +12,10 @@
     <sheet name="k4" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="k5" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="k6" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="k7" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="k8" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="k9" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="k10" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4336,4 +4340,5556 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.168586387434555</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.8346153846153846</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.2015503875968992</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.02179487179487179</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.01550387596899225</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.9461538461538461</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.3416149068322981</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.06201550387596899</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.3974358974358974</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.2403100775193799</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.4346153846153846</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.09489634832188296</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7.069047619047619</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.6177223888055972</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.2721107395020439</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.05984970477724101</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.01806380982170785</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8293807641633728</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.06357758620689655</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1008878573533746</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.1588564692012968</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.0429192455054524</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.2833038608900678</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>105</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.04826732673267327</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1714285714285714</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4571428571428571</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0761904761904762</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.580952380952381</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.009523809523809525</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4190476190476191</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.5428571428571428</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1714285714285714</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.08571428571428572</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.0380952380952381</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.0380952380952381</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.3619047619047619</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.009523809523809525</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.3818181818181818</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.006756756756756757</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.4527027027027027</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.2428571428571429</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>452</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0406987613928488</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6.236111111111111</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1792035398230089</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1106194690265487</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4601769911504425</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1991150442477876</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6128318584070797</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.09955752212389381</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.02433628318584071</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1946902654867257</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1061946902654867</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.2765486725663717</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1061946902654867</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.02654867256637168</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.07079646017699115</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.3517699115044248</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.2079646017699115</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.02433628318584071</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.004424778761061947</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.7477876106194691</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.07300884955752213</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.01106194690265487</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.002212389380530973</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.04867256637168142</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.05088495575221239</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.5603864734299517</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.08248299319727889</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.863961038961039</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.03137254901960784</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.05941176470588236</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.2562119081106423</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>236</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>434</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0476823102243035</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2096774193548387</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2027649769585254</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4354838709677419</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2465437788018433</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6935483870967742</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.02304147465437788</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.03917050691244239</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1543778801843318</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.3755760368663594</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.9654377880184332</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.0576036866359447</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.0576036866359447</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.3294930875576037</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.108294930875576</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.002304147465437788</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.6175115207373272</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.04147465437788019</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.01382488479262673</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.006912442396313364</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.04608294930875576</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.07603686635944701</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.3628663003663004</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.1335271317829457</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.3261157927590512</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.1206060606060606</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1274828457927049</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>172</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>111</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>43</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.05226480836236934</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.165938864628821</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8.444444444444445</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.5723684210526315</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.1907894736842105</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.03289473684210526</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1776315789473684</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.006578947368421052</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.1842105263157895</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.1710526315789474</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.168586387434555</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.8346153846153846</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.2015503875968992</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.02179487179487179</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.01550387596899225</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.9461538461538461</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.3416149068322981</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.06201550387596899</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.3974358974358974</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.2403100775193799</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.4346153846153846</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.09489634832188296</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7.069047619047619</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.6177223888055972</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.2721107395020439</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.05984970477724101</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.01806380982170785</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8293807641633728</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.06357758620689655</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1008878573533746</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.1588564692012968</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.0429192455054524</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.2833038608900678</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>105</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.04826732673267327</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1714285714285714</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4571428571428571</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0761904761904762</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.580952380952381</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.009523809523809525</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4190476190476191</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.5428571428571428</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1714285714285714</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.08571428571428572</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.0380952380952381</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.0380952380952381</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.3619047619047619</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.009523809523809525</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.3818181818181818</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.006756756756756757</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.4527027027027027</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.2428571428571429</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>452</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0406987613928488</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6.236111111111111</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1792035398230089</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1106194690265487</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4601769911504425</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1991150442477876</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6128318584070797</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.09955752212389381</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.02433628318584071</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1946902654867257</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1061946902654867</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.2765486725663717</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1061946902654867</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.02654867256637168</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.07079646017699115</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.3517699115044248</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.2079646017699115</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.02433628318584071</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.004424778761061947</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.7477876106194691</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.07300884955752213</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.01106194690265487</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.002212389380530973</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.04867256637168142</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.05088495575221239</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.5603864734299517</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.08248299319727889</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.863961038961039</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.03137254901960784</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.05941176470588236</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.2562119081106423</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>236</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>23</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1520736860823692</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7.968253968253968</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.737424924924925</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.1434559559559559</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.07063313313313313</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.0360985985985986</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.7616991991991993</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.3517892892892893</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.3390265265265265</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.6908158158158159</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.01276276276276277</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.057494994994995</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>432</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.04745755335656381</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2106481481481481</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2037037037037037</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2453703703703704</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6967592592592593</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.02314814814814815</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.03935185185185185</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1550925925925926</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.4282407407407408</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.3726851851851852</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.9652777777777778</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05324074074074074</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.05787037037037037</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3287037037037037</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1041666666666667</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.002314814814814815</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.6180555555555556</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.006944444444444444</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.04629629629629629</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.3633658008658008</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.3261157927590512</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.1216920334567393</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1293199554069119</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>111</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>43</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.05226480836236934</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>18</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.165938864628821</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8.444444444444445</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.5723684210526315</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.1907894736842105</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.03289473684210526</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.1776315789473684</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.006578947368421052</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.1842105263157895</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.1710526315789474</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.168586387434555</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.8346153846153846</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.2015503875968992</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.02179487179487179</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.01550387596899225</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.9461538461538461</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.3416149068322981</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.06201550387596899</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.3974358974358974</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.2403100775193799</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.4346153846153846</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1278972979894993</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7.603386809269162</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.7125248077400149</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.3471378069957827</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.06826779955346068</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.007194244604316546</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.7998325477548995</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.2247736293723642</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1851742743736046</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.4099479037459687</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.03959935499875961</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.2166956090300173</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.09165469771530377</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7.069047619047619</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.5834700574241181</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.2721107395020439</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.05984970477724101</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.02240802675585284</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8293807641633728</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.0621141975308642</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.08946137719722624</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.1342437755481234</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.04809708111594904</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.300332383665717</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>105</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.04826732673267327</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1714285714285714</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4571428571428571</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0761904761904762</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.580952380952381</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.009523809523809525</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4190476190476191</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.5428571428571428</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1714285714285714</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.08571428571428572</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0380952380952381</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.0380952380952381</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.3619047619047619</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.009523809523809525</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.3818181818181818</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.006756756756756757</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.4527027027027027</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.2428571428571429</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>452</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0406987613928488</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6.236111111111111</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1792035398230089</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1106194690265487</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4601769911504425</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1991150442477876</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6128318584070797</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.09955752212389381</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.02433628318584071</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1946902654867257</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1061946902654867</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.2765486725663717</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1061946902654867</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.02654867256637168</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.07079646017699115</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.3517699115044248</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.2079646017699115</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.02433628318584071</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.004424778761061947</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.7477876106194691</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.07300884955752213</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.01106194690265487</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.002212389380530973</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.04867256637168142</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.05088495575221239</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5603864734299517</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.08248299319727889</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.863961038961039</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.03137254901960784</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.05941176470588236</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.2562119081106423</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>236</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>23</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1520736860823692</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7.968253968253968</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.737424924924925</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.1434559559559559</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.07063313313313313</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.0360985985985986</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.7616991991991993</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.3517892892892893</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.3390265265265265</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.6908158158158159</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.01276276276276277</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.057494994994995</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>432</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.04745755335656381</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2106481481481481</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2037037037037037</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2453703703703704</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6967592592592593</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.02314814814814815</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.03935185185185185</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1550925925925926</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.4282407407407408</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.3726851851851852</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.9652777777777778</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.05324074074074074</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.05787037037037037</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.3287037037037037</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.1041666666666667</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.002314814814814815</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.6180555555555556</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.006944444444444444</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.04629629629629629</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.3633658008658008</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.3261157927590512</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.1216920334567393</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1293199554069119</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>111</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>43</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.05226480836236934</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>18</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.165938864628821</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8.444444444444445</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.5723684210526315</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.1907894736842105</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.03289473684210526</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.1776315789473684</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.006578947368421052</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.1842105263157895</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.1710526315789474</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.168586387434555</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.8346153846153846</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.2015503875968992</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.02179487179487179</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.01550387596899225</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.9461538461538461</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.3416149068322981</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.06201550387596899</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.3974358974358974</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.2403100775193799</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.4346153846153846</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1278972979894993</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7.603386809269162</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.7125248077400149</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.3471378069957827</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.06826779955346068</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.007194244604316546</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.7998325477548995</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.2247736293723642</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1851742743736046</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.4099479037459687</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.03959935499875961</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.2166956090300173</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.09165469771530377</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7.069047619047619</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.5834700574241181</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.2721107395020439</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.05984970477724101</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.02240802675585284</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8293807641633728</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.0621141975308642</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.08946137719722624</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.1342437755481234</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.04809708111594904</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.300332383665717</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>45</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.201219512195122</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04444444444444445</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.04444444444444445</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.02222222222222222</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.9555555555555556</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.3555555555555556</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.8444444444444444</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.3111111111111111</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.04444444444444445</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.04444444444444445</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.02222222222222222</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.08888888888888889</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.9177215189873418</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.1554054054054054</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.01818181818181818</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.9448818897637795</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.4453125</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.04395604395604396</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.5074626865671642</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.4017857142857143</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.02209321241205417</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5.416666666666666</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2166666666666667</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.7833333333333333</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.3166666666666667</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.8708333333333333</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.8047619047619048</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.8979416809605489</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.575187969924812</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.553639846743295</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>452</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0406987613928488</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6.236111111111111</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1792035398230089</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1106194690265487</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4601769911504425</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1991150442477876</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6128318584070797</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.09955752212389381</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.02433628318584071</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1946902654867257</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1061946902654867</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.2765486725663717</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1061946902654867</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.02654867256637168</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.07079646017699115</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3517699115044248</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.2079646017699115</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.02433628318584071</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.004424778761061947</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.7477876106194691</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.07300884955752213</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.01106194690265487</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.002212389380530973</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.04867256637168142</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.05088495575221239</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5603864734299517</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.08248299319727889</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.863961038961039</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.03137254901960784</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.05941176470588236</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.2562119081106423</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>236</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>23</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1520736860823692</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7.968253968253968</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.737424924924925</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.1434559559559559</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.07063313313313313</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.0360985985985986</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.7616991991991993</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.3517892892892893</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.3390265265265265</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.6908158158158159</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.01276276276276277</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.057494994994995</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>432</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.04745755335656381</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2106481481481481</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2037037037037037</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2453703703703704</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6967592592592593</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02314814814814815</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.03935185185185185</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1550925925925926</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.4282407407407408</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.3726851851851852</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.9652777777777778</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.05324074074074074</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.05787037037037037</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.3287037037037037</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.1041666666666667</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.002314814814814815</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.6180555555555556</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.006944444444444444</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.04629629629629629</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.3633658008658008</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.3261157927590512</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.1216920334567393</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1293199554069119</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>111</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>43</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.05226480836236934</v>
+      </c>
+      <c r="E10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.165938864628821</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8.444444444444445</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.5723684210526315</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.1907894736842105</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.03289473684210526</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.1776315789473684</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.006578947368421052</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.1842105263157895</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.1710526315789474</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>